--- a/research/traditional_assets/database/data/uganda/uganda_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/uganda/uganda_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06570000000000001</v>
+        <v>0.0771</v>
       </c>
       <c r="E2">
-        <v>0.0725</v>
+        <v>0.0906</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,82 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>75.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="L2">
-        <v>0.3387024608501119</v>
+        <v>0.3252319929297393</v>
       </c>
       <c r="M2">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.08078431372549019</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.4081902245706737</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.08078431372549019</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.4081902245706737</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>210.5</v>
+        <v>283</v>
       </c>
       <c r="V2">
-        <v>0.550326797385621</v>
+        <v>0.9751895244658856</v>
       </c>
       <c r="W2">
-        <v>0.2266467065868264</v>
+        <v>0.1838621034224331</v>
       </c>
       <c r="X2">
-        <v>0.0811243197433322</v>
+        <v>0.120792752452267</v>
       </c>
       <c r="Y2">
-        <v>0.1455223868434942</v>
+        <v>0.06306935097016618</v>
       </c>
       <c r="Z2">
-        <v>1.579505300353357</v>
+        <v>0.7806140048292516</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07448591413610617</v>
+        <v>0.1117611719678351</v>
       </c>
       <c r="AC2">
-        <v>-0.07448591413610617</v>
+        <v>-0.1117611719678351</v>
       </c>
       <c r="AD2">
-        <v>100.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>100.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>-110.4</v>
+        <v>-199.9</v>
       </c>
       <c r="AH2">
-        <v>0.2074181516784086</v>
+        <v>0.2226091615322797</v>
       </c>
       <c r="AI2">
-        <v>0.2000399680255795</v>
+        <v>0.1649791542584872</v>
       </c>
       <c r="AJ2">
-        <v>-0.4057331863285557</v>
+        <v>-2.21373200442968</v>
       </c>
       <c r="AK2">
-        <v>-0.3808209727492239</v>
+        <v>-0.9057544177616674</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06570000000000001</v>
+        <v>0.0771</v>
       </c>
       <c r="E3">
-        <v>0.0725</v>
+        <v>0.0906</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +725,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>75.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="L3">
-        <v>0.3387024608501119</v>
+        <v>0.3252319929297393</v>
       </c>
       <c r="M3">
-        <v>30.9</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.08078431372549019</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.4081902245706737</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>30.9</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.08078431372549019</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.4081902245706737</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>210.5</v>
+        <v>283</v>
       </c>
       <c r="V3">
-        <v>0.550326797385621</v>
+        <v>0.9751895244658856</v>
       </c>
       <c r="W3">
-        <v>0.2266467065868264</v>
+        <v>0.1838621034224331</v>
       </c>
       <c r="X3">
-        <v>0.0811243197433322</v>
+        <v>0.120792752452267</v>
       </c>
       <c r="Y3">
-        <v>0.1455223868434942</v>
+        <v>0.06306935097016618</v>
       </c>
       <c r="Z3">
-        <v>1.579505300353357</v>
+        <v>0.7806140048292516</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07448591413610617</v>
+        <v>0.1117611719678351</v>
       </c>
       <c r="AC3">
-        <v>-0.07448591413610617</v>
+        <v>-0.1117611719678351</v>
       </c>
       <c r="AD3">
-        <v>100.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>100.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>-110.4</v>
+        <v>-199.9</v>
       </c>
       <c r="AH3">
-        <v>0.2074181516784086</v>
+        <v>0.2226091615322797</v>
       </c>
       <c r="AI3">
-        <v>0.2000399680255795</v>
+        <v>0.1649791542584872</v>
       </c>
       <c r="AJ3">
-        <v>-0.4057331863285557</v>
+        <v>-2.21373200442968</v>
       </c>
       <c r="AK3">
-        <v>-0.3808209727492239</v>
+        <v>-0.9057544177616674</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/uganda/uganda_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/uganda/uganda_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0771</v>
+        <v>0.117</v>
       </c>
       <c r="E2">
-        <v>0.0906</v>
+        <v>0.145</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,82 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>73.59999999999999</v>
+        <v>143.6</v>
       </c>
       <c r="L2">
-        <v>0.3252319929297393</v>
+        <v>0.4085348506401139</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>34.12</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.06960424316605468</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.2376044568245125</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>34.12</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.06960424316605468</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.2376044568245125</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>283</v>
+        <v>260.8</v>
       </c>
       <c r="V2">
-        <v>0.9751895244658856</v>
+        <v>0.5320277437780497</v>
       </c>
       <c r="W2">
-        <v>0.1838621034224331</v>
+        <v>0.2462466674146618</v>
       </c>
       <c r="X2">
-        <v>0.120792752452267</v>
+        <v>0.09725776747011047</v>
       </c>
       <c r="Y2">
-        <v>0.06306935097016618</v>
+        <v>0.1489888999445513</v>
       </c>
       <c r="Z2">
-        <v>0.7806140048292516</v>
+        <v>1.123864944366287</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1117611719678351</v>
+        <v>0.09249084845368617</v>
       </c>
       <c r="AC2">
-        <v>-0.1117611719678351</v>
+        <v>-0.09249084845368617</v>
       </c>
       <c r="AD2">
-        <v>83.09999999999999</v>
+        <v>104.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>83.09999999999999</v>
+        <v>104.7</v>
       </c>
       <c r="AG2">
-        <v>-199.9</v>
+        <v>-156.1</v>
       </c>
       <c r="AH2">
-        <v>0.2226091615322797</v>
+        <v>0.1759959657085224</v>
       </c>
       <c r="AI2">
-        <v>0.1649791542584872</v>
+        <v>0.1333248440086591</v>
       </c>
       <c r="AJ2">
-        <v>-2.21373200442968</v>
+        <v>-0.4672253816222686</v>
       </c>
       <c r="AK2">
-        <v>-0.9057544177616674</v>
+        <v>-0.2976167778836987</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0771</v>
+        <v>0.117</v>
       </c>
       <c r="E3">
-        <v>0.0906</v>
+        <v>0.145</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,87 +728,206 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>73.59999999999999</v>
+        <v>107.9</v>
       </c>
       <c r="L3">
-        <v>0.3252319929297393</v>
+        <v>0.3685109289617486</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>27.3</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.06337047353760446</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2530120481927711</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>27.3</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06337047353760446</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2530120481927711</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>283</v>
+        <v>195.2</v>
       </c>
       <c r="V3">
-        <v>0.9751895244658856</v>
+        <v>0.4531104921077065</v>
       </c>
       <c r="W3">
-        <v>0.1838621034224331</v>
+        <v>0.2565382786495483</v>
       </c>
       <c r="X3">
-        <v>0.120792752452267</v>
+        <v>0.09561821634734066</v>
       </c>
       <c r="Y3">
-        <v>0.06306935097016618</v>
+        <v>0.1609200623022076</v>
       </c>
       <c r="Z3">
-        <v>0.7806140048292516</v>
+        <v>1.326687811508835</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1117611719678351</v>
+        <v>0.09189461458441299</v>
       </c>
       <c r="AC3">
-        <v>-0.1117611719678351</v>
+        <v>-0.09189461458441299</v>
       </c>
       <c r="AD3">
-        <v>83.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>83.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>-199.9</v>
+        <v>-108.1</v>
       </c>
       <c r="AH3">
-        <v>0.2226091615322797</v>
+        <v>0.1681791851708824</v>
       </c>
       <c r="AI3">
-        <v>0.1649791542584872</v>
+        <v>0.1505878284923928</v>
       </c>
       <c r="AJ3">
-        <v>-2.21373200442968</v>
+        <v>-0.3349860551595909</v>
       </c>
       <c r="AK3">
-        <v>-0.9057544177616674</v>
+        <v>-0.282098121085595</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bank of Baroda (Uganda) Limited (UGSE:BOBU)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>35.7</v>
+      </c>
+      <c r="L4">
+        <v>0.6081771720613288</v>
+      </c>
+      <c r="M4">
+        <v>6.82</v>
+      </c>
+      <c r="N4">
+        <v>0.1148148148148148</v>
+      </c>
+      <c r="O4">
+        <v>0.1910364145658263</v>
+      </c>
+      <c r="P4">
+        <v>6.82</v>
+      </c>
+      <c r="Q4">
+        <v>0.1148148148148148</v>
+      </c>
+      <c r="R4">
+        <v>0.1910364145658263</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="V4">
+        <v>1.104377104377104</v>
+      </c>
+      <c r="W4">
+        <v>0.2359550561797753</v>
+      </c>
+      <c r="X4">
+        <v>0.09889731859288028</v>
+      </c>
+      <c r="Y4">
+        <v>0.137057737586895</v>
+      </c>
+      <c r="Z4">
+        <v>0.63762763415164</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.09308708232295936</v>
+      </c>
+      <c r="AC4">
+        <v>-0.09308708232295936</v>
+      </c>
+      <c r="AD4">
+        <v>17.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>17.6</v>
+      </c>
+      <c r="AG4">
+        <v>-47.99999999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AI4">
+        <v>0.08506524891251813</v>
+      </c>
+      <c r="AJ4">
+        <v>-4.210526315789471</v>
+      </c>
+      <c r="AK4">
+        <v>-0.3397027600849256</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>
